--- a/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
+++ b/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
@@ -1384,8 +1384,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71">
-        <v>93</v>
+      <c r="A71" t="str">
+        <v>0093</v>
       </c>
       <c r="B71" t="str">
         <v>SABINAS HIDALGO</v>

--- a/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
+++ b/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
@@ -740,8 +740,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>31</v>
+      <c r="A25" t="str">
+        <v>0031</v>
       </c>
       <c r="B25" t="str">
         <v>LAGOS DE MORENO</v>

--- a/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
+++ b/public/CLAVES_ETRANSPORTE/OFICINAS NOMENCLATURAS.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1117"/>
+  <dimension ref="A1:D1118"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16041,9 +16041,23 @@
         <v>GOLFO-FUTURA GOLFO</v>
       </c>
     </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v>1501</v>
+      </c>
+      <c r="B1118" t="str">
+        <v>AG. CENTRAL CAMIONERA NORTE</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>CCF</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>PAQUETERIA AG.METROPOLITANA-PAQUETERIA</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1118"/>
   </ignoredErrors>
 </worksheet>
 </file>